--- a/output/pdf_financials_xlsx/WML.xlsx
+++ b/output/pdf_financials_xlsx/WML.xlsx
@@ -5950,43 +5950,43 @@
         <v>6.202848</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.304863</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.347263</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.347263</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>6.976818</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>9.35988</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>11.353708</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>16.393317</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>18.982728</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>20.957309</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>23.990877</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>26.633001</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>28.139564</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>28.707895</v>
       </c>
     </row>
     <row r="93">
@@ -7428,10 +7428,10 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.038159</v>
+        <v>-0.321689</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>1.726322</v>
+        <v>1.454248</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0.272074</v>
@@ -7440,19 +7440,19 @@
         <v>0.0204</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.57661</v>
+        <v>0.519975</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>3.284623</v>
+        <v>-1.850547</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>15.512886</v>
+        <v>4.830692</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>31.480828</v>
+        <v>21.344556</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>11.814646</v>
+        <v>7.863421</v>
       </c>
       <c r="N118" s="3" t="n">
         <v>2.012151</v>
@@ -7464,7 +7464,7 @@
         <v>0.557611</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>40.605347</v>
+        <v>40.595347</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>1.392</v>
@@ -9816,7 +9816,11 @@
           <t>Share-based payment reserve (Notes 6 and 7)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -10992,7 +10996,11 @@
           <t>Share-based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -12592,7 +12600,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -13919,7 +13931,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -14323,7 +14339,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -14525,7 +14545,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -15420,7 +15444,11 @@
           <t>Share-based payment reserve (note 8)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -16222,7 +16250,11 @@
           <t>Share-based payment reserve (note 9)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -16931,7 +16963,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -20835,7 +20871,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -43979,7 +44019,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -47512,7 +47556,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WML.xlsx
+++ b/output/pdf_financials_xlsx/WML.xlsx
@@ -1035,13 +1035,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.038715</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.015687</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001017</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1973,13 +1973,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.572163</v>
+        <v>-6.610878</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.836491</v>
+        <v>-5.852178</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.537</v>
+        <v>-4.538017</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-6.22935</v>
@@ -2089,13 +2089,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.572163</v>
+        <v>-6.610878</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.836491</v>
+        <v>-5.852178</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.537</v>
+        <v>-4.538017</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-6.22935</v>
@@ -2396,55 +2396,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.226244</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.760657</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.867582</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.014918</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.07066</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.007057</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.004946</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.096887</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.988156</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.474738</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.636166</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.378301</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>4.260508</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>5.272191</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>4.695793</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.412674</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.470901</v>
       </c>
     </row>
     <row r="35">
@@ -2512,55 +2512,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.226244</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.760657</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.867582</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.014918</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.07066</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.007057</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.004946</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.096887</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.988156</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.474738</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.636166</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.378301</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>4.260508</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>5.272191</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.37</v>
+        <v>5.065793</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>1.977242</v>
+        <v>3.389916</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.989879</v>
+        <v>1.46078</v>
       </c>
     </row>
     <row r="37">
@@ -3208,55 +3208,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.254825</v>
+        <v>0.028581</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.789582</v>
+        <v>0.028925</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.642626</v>
+        <v>0.775044</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.075017</v>
+        <v>0.060099</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.158048</v>
+        <v>0.08738799999999999</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.035078</v>
+        <v>0.028021</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.026112</v>
+        <v>0.021166</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.132803</v>
+        <v>0.035916</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.250323</v>
+        <v>0.262167</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.580491</v>
+        <v>0.105753</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.107487</v>
+        <v>0.471321</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.016312</v>
+        <v>0.638011</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.907583</v>
+        <v>0.647075</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>5.52979</v>
+        <v>0.257599</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>5.364822</v>
+        <v>0.669029</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.714172</v>
+        <v>0.301498</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.73548</v>
+        <v>0.264579</v>
       </c>
     </row>
     <row r="49">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -73855,7 +73855,7 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E656" s="5" t="n">

--- a/output/pdf_financials_xlsx/WML.xlsx
+++ b/output/pdf_financials_xlsx/WML.xlsx
@@ -1315,7 +1315,7 @@
         <v>-52.220282</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-6.027968</v>
+        <v>-5.980854</v>
       </c>
     </row>
     <row r="17">
@@ -1373,7 +1373,7 @@
         <v>-0</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.047114</v>
       </c>
     </row>
     <row r="18">
@@ -2021,7 +2021,7 @@
         <v>-52.220282</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-6.027968</v>
+        <v>-5.980854</v>
       </c>
     </row>
     <row r="28">
@@ -2137,7 +2137,7 @@
         <v>-52.220282</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-6.027968</v>
+        <v>-5.980854</v>
       </c>
     </row>
     <row r="30">
@@ -2287,7 +2287,7 @@
         <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.7877470341192078</v>
       </c>
     </row>
     <row r="32">
@@ -6964,10 +6964,10 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.057914</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.151061</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -6988,13 +6988,13 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.215621</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.014407</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.004869</v>
       </c>
       <c r="P110" s="3" t="n">
         <v>0</v>
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.036572</v>
       </c>
     </row>
     <row r="111">
@@ -7013,16 +7013,16 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01706</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002631</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003388</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00556</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -7037,13 +7037,13 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003444</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.017898</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002162</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
@@ -7293,7 +7293,7 @@
         <v>0</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.522355</v>
       </c>
     </row>
     <row r="116">
@@ -8381,16 +8381,16 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01706</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002631</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003388</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00556</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -8405,13 +8405,13 @@
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003444</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.017898</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002162</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
@@ -8439,16 +8439,16 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.452627</v>
+        <v>-1.469687</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.562407</v>
+        <v>-1.565038</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.631223</v>
+        <v>-1.634611</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-4.95413</v>
+        <v>-4.95969</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-0.864569</v>
@@ -8463,13 +8463,13 @@
         <v>-1.573989</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-4.322917</v>
+        <v>-4.326361</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-6.74988</v>
+        <v>-6.767778</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-6.761955</v>
+        <v>-6.764117</v>
       </c>
       <c r="M135" s="3" t="n">
         <v>-4.973925</v>
@@ -19179,7 +19179,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -20068,7 +20072,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -20770,7 +20778,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -27293,7 +27305,11 @@
           <t>Private placements 21,464,817 5,173,055 204,445</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -29107,7 +29123,11 @@
           <t>Derivative liability on private placement $</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -31006,7 +31026,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E229" s="5" t="n">
         <v>-0.01706</v>
       </c>
@@ -58958,7 +58982,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
           <t>-</t>
